--- a/Result/profitability/3717.xlsx
+++ b/Result/profitability/3717.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,6 +1200,129 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3717</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1682</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1313</v>
+      </c>
+      <c r="E7" t="n">
+        <v>370</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="G7" t="n">
+        <v>166</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9.90%</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J7" t="n">
+        <v>148</v>
+      </c>
+      <c r="K7" t="n">
+        <v>142</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2100000000000001</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.446808510638298</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.710000000000001</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2.283018867924528</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4761584956346541</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
